--- a/public/assets/Kurly-template.xlsx
+++ b/public/assets/Kurly-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45CD2C71-B558-433A-871C-96A0ABED3348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42038D47-D7C6-4396-98FC-A0BBF792BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4EC0EFCC-873D-CF47-B1E6-865BEEA70AA4}"/>
   </bookViews>
@@ -198,7 +198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -234,8 +234,22 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,6 +266,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -323,7 +343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -343,6 +363,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,13 +715,13 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -701,7 +730,7 @@
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -710,10 +739,10 @@
       <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="9" t="s">
         <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -737,7 +766,7 @@
       <c r="V1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="X1" s="1" t="s">
@@ -758,13 +787,13 @@
       <c r="AC1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="7" t="s">
         <v>34</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="7" t="s">
         <v>33</v>
       </c>
       <c r="AG1" s="1" t="s">
